--- a/NEW_HIRE_MAS_Scores.xlsx
+++ b/NEW_HIRE_MAS_Scores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{128FBD8C-FC78-4FE1-8893-76F3D70D6FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4510605D-47B9-4308-928F-53E04ED01ADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-50" yWindow="0" windowWidth="26580" windowHeight="13770" xr2:uid="{1898A9E1-10FE-406B-A3BC-4C7125C840EB}"/>
+    <workbookView xWindow="1060" yWindow="1080" windowWidth="29330" windowHeight="13660" xr2:uid="{1898A9E1-10FE-406B-A3BC-4C7125C840EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -831,13 +831,13 @@
         <v>3</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>6</v>

--- a/NEW_HIRE_MAS_Scores.xlsx
+++ b/NEW_HIRE_MAS_Scores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4510605D-47B9-4308-928F-53E04ED01ADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23426BAD-8E64-471F-8B65-A443DCF56DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1060" yWindow="1080" windowWidth="29330" windowHeight="13660" xr2:uid="{1898A9E1-10FE-406B-A3BC-4C7125C840EB}"/>
+    <workbookView xWindow="14230" yWindow="60" windowWidth="20640" windowHeight="13660" xr2:uid="{1898A9E1-10FE-406B-A3BC-4C7125C840EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="17">
   <si>
     <t>Doni Lantow</t>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t>ReviewYear</t>
+  </si>
+  <si>
+    <t>August</t>
   </si>
 </sst>
 </file>
@@ -484,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{139554F0-8ABC-4CD8-817E-E6CB5E4FC3E3}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultColWidth="20.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
@@ -492,10 +495,10 @@
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23.54296875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.7265625" customWidth="1"/>
-    <col min="7" max="7" width="13.7265625" customWidth="1"/>
-    <col min="8" max="8" width="15.6328125" customWidth="1"/>
-    <col min="9" max="9" width="13.26953125" customWidth="1"/>
+    <col min="6" max="6" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.35">
@@ -831,13 +834,13 @@
         <v>3</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G12" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>6</v>
@@ -860,13 +863,13 @@
         <v>2</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>6</v>
@@ -988,6 +991,122 @@
         <v>6</v>
       </c>
       <c r="I17" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="2">
+        <v>46234</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="1">
+        <v>100</v>
+      </c>
+      <c r="G18" s="3">
+        <v>1</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I18" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="2">
+        <v>46234</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I19" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="2">
+        <v>46240</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="2">
+        <v>46241</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F21" s="1">
+        <v>100</v>
+      </c>
+      <c r="G21" s="3">
+        <v>1</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" s="1">
         <v>2026</v>
       </c>
     </row>

--- a/NEW_HIRE_MAS_Scores.xlsx
+++ b/NEW_HIRE_MAS_Scores.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23426BAD-8E64-471F-8B65-A443DCF56DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FFC1C41-D36E-49FE-BE2D-D435484A2293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14230" yWindow="60" windowWidth="20640" windowHeight="13660" xr2:uid="{1898A9E1-10FE-406B-A3BC-4C7125C840EB}"/>
+    <workbookView xWindow="18520" yWindow="350" windowWidth="15950" windowHeight="13660" xr2:uid="{1898A9E1-10FE-406B-A3BC-4C7125C840EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="20">
   <si>
     <t>Doni Lantow</t>
   </si>
@@ -90,6 +90,15 @@
   </si>
   <si>
     <t>August</t>
+  </si>
+  <si>
+    <t>Terra McGee</t>
+  </si>
+  <si>
+    <t>Charles</t>
+  </si>
+  <si>
+    <t>Tiffany Lewis</t>
   </si>
 </sst>
 </file>
@@ -120,15 +129,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -136,12 +151,49 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -150,6 +202,36 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -487,7 +569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{139554F0-8ABC-4CD8-817E-E6CB5E4FC3E3}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultColWidth="20.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
@@ -1110,6 +1192,238 @@
         <v>2026</v>
       </c>
     </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="6">
+        <v>46245</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="5">
+        <v>100</v>
+      </c>
+      <c r="G22" s="7">
+        <v>1</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="8">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="11">
+        <v>46247</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F23" s="10">
+        <v>100</v>
+      </c>
+      <c r="G23" s="12">
+        <v>1</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" s="13">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="6">
+        <v>46246</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="5">
+        <v>100</v>
+      </c>
+      <c r="G24" s="7">
+        <v>1</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="8">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="11">
+        <v>46247</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F25" s="10">
+        <v>95</v>
+      </c>
+      <c r="G25" s="12">
+        <v>0.95</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" s="13">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" s="6">
+        <v>46245</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" s="5">
+        <v>100</v>
+      </c>
+      <c r="G26" s="7">
+        <v>1</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" s="8">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="11">
+        <v>46247</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" s="10">
+        <v>100</v>
+      </c>
+      <c r="G27" s="12">
+        <v>1</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" s="13">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="6">
+        <v>46247</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F28" s="5">
+        <v>100</v>
+      </c>
+      <c r="G28" s="7">
+        <v>1</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I28" s="8">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="11">
+        <v>46248</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F29" s="10">
+        <v>100</v>
+      </c>
+      <c r="G29" s="12">
+        <v>1</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I29" s="13">
+        <v>2026</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/NEW_HIRE_MAS_Scores.xlsx
+++ b/NEW_HIRE_MAS_Scores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FFC1C41-D36E-49FE-BE2D-D435484A2293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1471069-BE26-41FF-90B0-0696DF406033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18520" yWindow="350" windowWidth="15950" windowHeight="13660" xr2:uid="{1898A9E1-10FE-406B-A3BC-4C7125C840EB}"/>
+    <workbookView xWindow="12470" yWindow="0" windowWidth="18220" windowHeight="13660" xr2:uid="{1898A9E1-10FE-406B-A3BC-4C7125C840EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="20">
   <si>
     <t>Doni Lantow</t>
   </si>
@@ -569,7 +569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{139554F0-8ABC-4CD8-817E-E6CB5E4FC3E3}">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr defaultColWidth="20.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
@@ -1424,6 +1424,93 @@
         <v>2026</v>
       </c>
     </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="2">
+        <v>46251</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F30" s="1">
+        <v>100</v>
+      </c>
+      <c r="G30" s="3">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I30" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="2">
+        <v>46251</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F31" s="1">
+        <v>0</v>
+      </c>
+      <c r="G31" s="3">
+        <v>0</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A32" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32" s="2">
+        <v>46251</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="1">
+        <v>90</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" s="1">
+        <v>2026</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/NEW_HIRE_MAS_Scores.xlsx
+++ b/NEW_HIRE_MAS_Scores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1471069-BE26-41FF-90B0-0696DF406033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3DFBB04-CBDD-4CC7-9FFA-C3985584D1BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12470" yWindow="0" windowWidth="18220" windowHeight="13660" xr2:uid="{1898A9E1-10FE-406B-A3BC-4C7125C840EB}"/>
+    <workbookView xWindow="20976" yWindow="48" windowWidth="19884" windowHeight="16452" xr2:uid="{1898A9E1-10FE-406B-A3BC-4C7125C840EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="21">
   <si>
     <t>Doni Lantow</t>
   </si>
@@ -99,6 +99,9 @@
   </si>
   <si>
     <t>Tiffany Lewis</t>
+  </si>
+  <si>
+    <t>Connor Floriani</t>
   </si>
 </sst>
 </file>
@@ -569,21 +572,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{139554F0-8ABC-4CD8-817E-E6CB5E4FC3E3}">
-  <dimension ref="A1:I32"/>
-  <sheetFormatPr defaultColWidth="20.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I36"/>
+  <sheetFormatPr defaultColWidth="20.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -612,7 +615,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -641,7 +644,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -670,7 +673,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -699,7 +702,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -728,7 +731,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -757,7 +760,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -786,7 +789,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
@@ -815,7 +818,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
@@ -844,7 +847,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -873,7 +876,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>5</v>
       </c>
@@ -902,7 +905,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
@@ -931,7 +934,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
@@ -960,7 +963,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>0</v>
       </c>
@@ -989,7 +992,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
@@ -1018,7 +1021,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>5</v>
       </c>
@@ -1047,7 +1050,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>5</v>
       </c>
@@ -1076,7 +1079,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>0</v>
       </c>
@@ -1105,7 +1108,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>5</v>
       </c>
@@ -1134,7 +1137,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>5</v>
       </c>
@@ -1163,7 +1166,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>0</v>
       </c>
@@ -1192,7 +1195,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>17</v>
       </c>
@@ -1221,7 +1224,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
         <v>17</v>
       </c>
@@ -1250,7 +1253,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>0</v>
       </c>
@@ -1279,7 +1282,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
         <v>0</v>
       </c>
@@ -1308,7 +1311,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>5</v>
       </c>
@@ -1337,7 +1340,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
         <v>5</v>
       </c>
@@ -1366,7 +1369,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>19</v>
       </c>
@@ -1395,7 +1398,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
         <v>19</v>
       </c>
@@ -1424,7 +1427,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>0</v>
       </c>
@@ -1453,7 +1456,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>5</v>
       </c>
@@ -1482,7 +1485,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>19</v>
       </c>
@@ -1508,6 +1511,122 @@
         <v>16</v>
       </c>
       <c r="I32" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" s="11">
+        <v>46255</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F33" s="10">
+        <v>100</v>
+      </c>
+      <c r="G33" s="12">
+        <v>1</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" s="13">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" s="6">
+        <v>46255</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F34" s="5">
+        <v>100</v>
+      </c>
+      <c r="G34" s="7">
+        <v>1</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34" s="8">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C35" s="11">
+        <v>46255</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F35" s="10">
+        <v>100</v>
+      </c>
+      <c r="G35" s="12">
+        <v>1</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" s="13">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="6">
+        <v>46261</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F36" s="5">
+        <v>100</v>
+      </c>
+      <c r="G36" s="7">
+        <v>1</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I36" s="8">
         <v>2026</v>
       </c>
     </row>

--- a/NEW_HIRE_MAS_Scores.xlsx
+++ b/NEW_HIRE_MAS_Scores.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3DFBB04-CBDD-4CC7-9FFA-C3985584D1BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E784A70-5F78-4D0A-899F-513E7D800FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20976" yWindow="48" windowWidth="19884" windowHeight="16452" xr2:uid="{1898A9E1-10FE-406B-A3BC-4C7125C840EB}"/>
+    <workbookView xWindow="26205" yWindow="0" windowWidth="25485" windowHeight="19800" xr2:uid="{1898A9E1-10FE-406B-A3BC-4C7125C840EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$36</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="22">
   <si>
     <t>Doni Lantow</t>
   </si>
@@ -102,6 +105,9 @@
   </si>
   <si>
     <t>Connor Floriani</t>
+  </si>
+  <si>
+    <t>September</t>
   </si>
 </sst>
 </file>
@@ -572,21 +578,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{139554F0-8ABC-4CD8-817E-E6CB5E4FC3E3}">
-  <dimension ref="A1:I36"/>
-  <sheetFormatPr defaultColWidth="20.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I38"/>
+  <sheetFormatPr defaultColWidth="20.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -615,7 +621,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -644,7 +650,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -673,7 +679,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -702,7 +708,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -731,7 +737,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -760,7 +766,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -789,7 +795,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
@@ -818,7 +824,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
@@ -847,7 +853,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -876,7 +882,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>5</v>
       </c>
@@ -905,7 +911,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
@@ -934,7 +940,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
@@ -963,7 +969,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>0</v>
       </c>
@@ -992,7 +998,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
@@ -1021,7 +1027,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>5</v>
       </c>
@@ -1050,7 +1056,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>5</v>
       </c>
@@ -1079,7 +1085,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>0</v>
       </c>
@@ -1108,7 +1114,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>5</v>
       </c>
@@ -1137,7 +1143,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>5</v>
       </c>
@@ -1166,7 +1172,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>0</v>
       </c>
@@ -1195,7 +1201,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>17</v>
       </c>
@@ -1224,7 +1230,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
         <v>17</v>
       </c>
@@ -1253,7 +1259,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>0</v>
       </c>
@@ -1282,7 +1288,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
         <v>0</v>
       </c>
@@ -1311,7 +1317,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>5</v>
       </c>
@@ -1340,7 +1346,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
         <v>5</v>
       </c>
@@ -1369,7 +1375,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>19</v>
       </c>
@@ -1398,7 +1404,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
         <v>19</v>
       </c>
@@ -1427,7 +1433,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>0</v>
       </c>
@@ -1456,7 +1462,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>5</v>
       </c>
@@ -1485,7 +1491,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>19</v>
       </c>
@@ -1514,7 +1520,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
         <v>0</v>
       </c>
@@ -1543,7 +1549,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>5</v>
       </c>
@@ -1572,7 +1578,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
         <v>19</v>
       </c>
@@ -1601,7 +1607,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>20</v>
       </c>
@@ -1630,7 +1636,66 @@
         <v>2026</v>
       </c>
     </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" s="2">
+        <v>46261</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F37" s="1">
+        <v>100</v>
+      </c>
+      <c r="G37" s="3">
+        <v>1</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I37" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="2">
+        <v>46267</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F38" s="1">
+        <v>90</v>
+      </c>
+      <c r="G38" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I38" s="1">
+        <v>2026</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:I36" xr:uid="{139554F0-8ABC-4CD8-817E-E6CB5E4FC3E3}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>